--- a/shadowedhistory/footnotes/series_log.xlsx
+++ b/shadowedhistory/footnotes/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1587,6 +1587,281 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-18 21:26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8a7d4b2c5b1f5f71038084ab017df994_1784409953.mp4</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep05/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-18 21:29</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ab72b35a77a677f3f19decb365f855a2_1784410103.mp4</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep05/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-18 21:36</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/38e01b752c16d399ecec667bb48b4057_1784410308.mp4</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep05/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-18 21:44</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/1af9ea2ab9fbc93abdc2c2fc4855fad2_1784410819.mp4</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep05/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-18 21:46</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7c0cf1f524f42f1851971d382d4b9d47_1784411142.mp4</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep05/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/footnotes/series_log.xlsx
+++ b/shadowedhistory/footnotes/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1862,6 +1862,281 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-19 21:36</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>315.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1.575</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c6aa8b4d4d7f9402b880e4fa1fdd635f_1784496374.mp4</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep06/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-19 21:39</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/cc5b02a99b1dd7e7ad6acc7a322f4d14_1784497140.mp4</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep06/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-19 21:43</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0c59a152a59fbd2037b22eb3716412ff_1784497420.mp4</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep06/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-19 21:46</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/307ef32314142b1ceddb79590f2d1801_1784497567.mp4</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep06/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-19 21:49</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8bd46a3bb3229d4f396f83e9f8f1be97_1784497726.mp4</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep06/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/footnotes/series_log.xlsx
+++ b/shadowedhistory/footnotes/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2137,6 +2137,281 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-20 21:45</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/65e49ade4b0779bec6b66aab3ee245d5_1784583866.mp4</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep07/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-20 21:47</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/cba59e16cc557b28cc25593b7d6dbcca_1784583994.mp4</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep07/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-20 21:49</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5c89d6c84527100a5ead70de9caf3bd6_1784584140.mp4</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep07/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-20 21:51</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c8eb58fd854dbca65eaf0ad369979c44_1784584268.mp4</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep07/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-20 21:54</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/cd5333e378478f046fde696cfd5f859a_1784584413.mp4</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep07/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/footnotes/series_log.xlsx
+++ b/shadowedhistory/footnotes/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2412,6 +2412,281 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-21 21:42</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/710daf71a22c35576f5ee5b9b8bd1880_1784670097.mp4</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep08/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-21 21:45</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/537a8ac561c66adfd780041c401140ce.mp4</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep08/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-21 21:51</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>315.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1.575</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ea471d5b8d09636e369b78e9254104c3_1784670412.mp4</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep08/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-21 21:56</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2b91b99c1635ff92c7c9c1fd14b57fca_1784670935.mp4</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep08/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-21 21:58</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/d89b660a7ca6ae8ae4e0112d9a6a7fb6.mp4</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep08/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/footnotes/series_log.xlsx
+++ b/shadowedhistory/footnotes/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2687,6 +2687,281 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:41</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ddf98075d6c480691a6b06e961ecf095_1784756330.mp4</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep09/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:45</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d34cf496bfd3eb60ba2c1ede5c0b5c37_1784756575.mp4</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep09/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:47</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c1dab72605d0011544ddf11f62ddce2b_1784756831.mp4</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep09/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:50</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7812c5d71a4c06a603ba3de35a7ec020_1784756973.mp4</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep09/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:52</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7bee876017914a7b496fb35c5887e54c_1784757099.mp4</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep09/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/footnotes/series_log.xlsx
+++ b/shadowedhistory/footnotes/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2962,6 +2962,281 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:42</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>315.0</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>1.575</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/4fec1f4bcf87651860687ac34f22ce0b_1784842628.mp4</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep10/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:45</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9c33300287d69760b3fae2e160c18a64_1784843106.mp4</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep10/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:48</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/84a416d640a2b46f8258460a76b89b4f_1784843268.mp4</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep10/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:50</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2f281ac28aadf6b4f3a7aa40ddd6eba0_1784843398.mp4</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep10/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-23 21:52</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6678e333dfb13fa130dac79cbb7898cc_1784843511.mp4</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep10/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/footnotes/series_log.xlsx
+++ b/shadowedhistory/footnotes/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3237,6 +3237,281 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-24 21:39</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/bfcb709e65d5925ed8b25daa0c743c5d_1784929157.mp4</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep11/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-24 21:42</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6e836119dbcb68d7ef2f99ed42bb9f93_1784929318.mp4</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep11/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-24 21:45</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ebe2d5c2cf2db08ce4f27b19211e7549_1784929473.mp4</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep11/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-24 21:49</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ded5cab15c1bf2815fc5dce7b8014852_1784929604.mp4</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep11/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-24 21:51</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a05173ffd896245c28ac7fda9137457b_1784929876.mp4</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep11/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/footnotes/series_log.xlsx
+++ b/shadowedhistory/footnotes/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3512,6 +3512,281 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-25 21:27</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/10d7d53842218fddd94bce6f5e48a308.mp4</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep12/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-25 21:30</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/53bfaee3281666416bea98aea633f044_1785014980.mp4</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep12/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-25 21:41</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>315.0</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>1.575</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ea6ffb7db5895087782c7701930aebd0_1785015211.mp4</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep12/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-25 21:50</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/c68db4f8832e566ef828948020ba479b.mp4</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep12/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-25 21:53</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/769773e9d41ab1e6052c3caa4c4c8c2d_1785016351.mp4</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep12/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/footnotes/series_log.xlsx
+++ b/shadowedhistory/footnotes/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3787,6 +3787,281 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-26 21:30</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/54026763fdebe709f03a576fc44442cb_1785101282.mp4</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep13/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-07-26 21:32</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/1eb65197da7bb80e1f5d134d2bc1ea0c_1785101540.mp4</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep13/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-07-26 21:35</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/29624ca0a5cd797e2178b6363224f61d_1785101671.mp4</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep13/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-07-26 21:39</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b2bedc8059699d85c07acb5daa02380b_1785101794.mp4</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep13/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-07-26 21:41</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/302377280d8e77a8c14118e4829afaac_1785102067.mp4</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/footnotes/episodes/ep13/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
